--- a/flights.xlsx
+++ b/flights.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T14:29:13+08:00</t>
+          <t>2026-09-22T14:38:03+08:00</t>
         </is>
       </c>
     </row>
